--- a/ROSA_vitaSPEC/CLUSTER/PRODUCTION/METRIQUES_PERFORMANCES_PLS.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/PRODUCTION/METRIQUES_PERFORMANCES_PLS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\AppData\Roaming\MobaXterm\slash\mx86_64b\RemoteFiles\5311686_2_2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\CLUSTER\PRODUCTION\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -493,9 +493,17 @@
   <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
